--- a/design.xlsx
+++ b/design.xlsx
@@ -681,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P25"/>
+  <dimension ref="B1:P29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="2" max="2"/>
@@ -791,7 +791,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="D7" s="26" t="inlineStr">
         <is>
@@ -1351,14 +1350,42 @@
       </c>
       <c r="K24" s="15" t="inlineStr">
         <is>
-          <t>Pick (R)</t>
+          <t>Wt (F)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="K25" s="17" t="inlineStr">
         <is>
+          <t>SEC1_WEIGHTFRONT</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="K26" s="15" t="inlineStr">
+        <is>
+          <t>Pick (R)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="K27" s="17" t="inlineStr">
+        <is>
           <t>SEC1_PICKREAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="K28" s="15" t="inlineStr">
+        <is>
+          <t>Wt (R)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="K29" s="17" t="inlineStr">
+        <is>
+          <t>SEC1_WEIGHTREAR</t>
         </is>
       </c>
     </row>
